--- a/database/event/6141/event_6141_evp_summary.xlsx
+++ b/database/event/6141/event_6141_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>8.7989</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8848</v>
+        <v>4.789</v>
       </c>
       <c r="E2" t="n">
         <v>13.1349</v>
@@ -514,7 +514,7 @@
         <v>6.6714</v>
       </c>
       <c r="H2" t="n">
-        <v>8.650399999999999</v>
+        <v>8.586</v>
       </c>
       <c r="I2" t="n">
         <v>8.7311</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.4251</v>
+        <v>9.402799999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>6.3137</v>
+        <v>6.2988</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3862</v>
+        <v>3.3022</v>
       </c>
       <c r="E3" t="n">
-        <v>9.4251</v>
+        <v>9.402799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4735</v>
+        <v>4.4512</v>
       </c>
       <c r="G3" t="n">
         <v>4.9516</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7114</v>
+        <v>4.6764</v>
       </c>
       <c r="I3" t="n">
         <v>4.7554</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.172700000000001</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>5.4748</v>
+        <v>5.4656</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8802</v>
+        <v>2.8066</v>
       </c>
       <c r="E4" t="n">
-        <v>8.172700000000001</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1439</v>
+        <v>5.1302</v>
       </c>
       <c r="G4" t="n">
         <v>3.0288</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7626</v>
+        <v>5.7411</v>
       </c>
       <c r="I4" t="n">
         <v>5.7895</v>
@@ -640,7 +640,7 @@
         <v>5.3018</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7759</v>
+        <v>2.7092</v>
       </c>
       <c r="E5" t="n">
         <v>7.9145</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.5343</v>
+        <v>7.5067</v>
       </c>
       <c r="C6" t="n">
-        <v>5.0471</v>
+        <v>5.0286</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6223</v>
+        <v>2.5468</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5343</v>
+        <v>7.5067</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1737</v>
+        <v>5.1462</v>
       </c>
       <c r="G6" t="n">
         <v>2.3606</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8094</v>
+        <v>5.7661</v>
       </c>
       <c r="I6" t="n">
         <v>5.8636</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.8231</v>
+        <v>6.8133</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5707</v>
+        <v>4.5641</v>
       </c>
       <c r="D7" t="n">
-        <v>2.335</v>
+        <v>2.2705</v>
       </c>
       <c r="E7" t="n">
-        <v>6.8231</v>
+        <v>6.8133</v>
       </c>
       <c r="F7" t="n">
-        <v>5.3456</v>
+        <v>5.0931</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4775</v>
+        <v>1.7202</v>
       </c>
       <c r="H7" t="n">
-        <v>6.0788</v>
+        <v>5.6828</v>
       </c>
       <c r="I7" t="n">
-        <v>6.1355</v>
+        <v>5.6828</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4775</v>
+        <v>1.7202</v>
       </c>
       <c r="K7" t="n">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="L7" t="n">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="M7" t="n">
-        <v>7.613</v>
+        <v>7.403</v>
       </c>
       <c r="N7" t="n">
-        <v>591</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.8133</v>
+        <v>6.7942</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5641</v>
+        <v>4.5513</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3311</v>
+        <v>2.2629</v>
       </c>
       <c r="E8" t="n">
-        <v>6.8133</v>
+        <v>6.7942</v>
       </c>
       <c r="F8" t="n">
-        <v>5.0931</v>
+        <v>5.3167</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7202</v>
+        <v>1.4775</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6828</v>
+        <v>6.0335</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6828</v>
+        <v>6.1355</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7202</v>
+        <v>1.4775</v>
       </c>
       <c r="K8" t="n">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="L8" t="n">
-        <v>165</v>
+        <v>279</v>
       </c>
       <c r="M8" t="n">
-        <v>7.403</v>
+        <v>7.613</v>
       </c>
       <c r="N8" t="n">
-        <v>428</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +824,7 @@
         <v>4.5141</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3009</v>
+        <v>2.2407</v>
       </c>
       <c r="E9" t="n">
         <v>6.7386</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.6578</v>
+        <v>6.6366</v>
       </c>
       <c r="C10" t="n">
-        <v>4.46</v>
+        <v>4.4458</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2682</v>
+        <v>2.2001</v>
       </c>
       <c r="E10" t="n">
-        <v>6.6578</v>
+        <v>6.6366</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3111</v>
+        <v>4.29</v>
       </c>
       <c r="G10" t="n">
         <v>2.3466</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4568</v>
+        <v>4.4236</v>
       </c>
       <c r="I10" t="n">
         <v>4.4984</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.4635</v>
+        <v>6.4548</v>
       </c>
       <c r="C11" t="n">
-        <v>4.3298</v>
+        <v>4.324</v>
       </c>
       <c r="D11" t="n">
-        <v>2.1897</v>
+        <v>2.1277</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4635</v>
+        <v>6.4548</v>
       </c>
       <c r="F11" t="n">
-        <v>6.4635</v>
+        <v>6.4548</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8473</v>
+        <v>7.818</v>
       </c>
       <c r="I11" t="n">
         <v>7.8838</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8622</v>
+        <v>5.8503</v>
       </c>
       <c r="C12" t="n">
-        <v>3.927</v>
+        <v>3.919</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9468</v>
+        <v>1.8868</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8622</v>
+        <v>5.8503</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1897</v>
+        <v>3.1778</v>
       </c>
       <c r="G12" t="n">
         <v>2.6725</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1897</v>
+        <v>3.1778</v>
       </c>
       <c r="I12" t="n">
         <v>3.2045</v>
@@ -1008,7 +1008,7 @@
         <v>3.9103</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9368</v>
+        <v>1.8817</v>
       </c>
       <c r="E13" t="n">
         <v>5.8373</v>
@@ -1054,7 +1054,7 @@
         <v>3.6708</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7924</v>
+        <v>1.7392</v>
       </c>
       <c r="E14" t="n">
         <v>5.4798</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.4409</v>
+        <v>5.4275</v>
       </c>
       <c r="C15" t="n">
-        <v>3.6448</v>
+        <v>3.6358</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7766</v>
+        <v>1.7184</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4409</v>
+        <v>5.4275</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0547</v>
+        <v>5.0413</v>
       </c>
       <c r="G15" t="n">
         <v>0.3862</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6227</v>
+        <v>5.6017</v>
       </c>
       <c r="I15" t="n">
         <v>5.6489</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.171</v>
+        <v>5.1572</v>
       </c>
       <c r="C16" t="n">
-        <v>3.464</v>
+        <v>3.4547</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6676</v>
+        <v>1.6107</v>
       </c>
       <c r="E16" t="n">
-        <v>5.171</v>
+        <v>5.1572</v>
       </c>
       <c r="F16" t="n">
-        <v>5.171</v>
+        <v>5.1572</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.805</v>
+        <v>5.7834</v>
       </c>
       <c r="I16" t="n">
         <v>5.832</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.1467</v>
+        <v>5.1163</v>
       </c>
       <c r="C17" t="n">
-        <v>3.4477</v>
+        <v>3.4273</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6578</v>
+        <v>1.5944</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1467</v>
+        <v>5.1163</v>
       </c>
       <c r="F17" t="n">
-        <v>5.55</v>
+        <v>5.5196</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4033</v>
       </c>
       <c r="H17" t="n">
-        <v>6.3994</v>
+        <v>6.3517</v>
       </c>
       <c r="I17" t="n">
         <v>6.4591</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.0533</v>
+        <v>5.0295</v>
       </c>
       <c r="C18" t="n">
-        <v>3.3851</v>
+        <v>3.3692</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6201</v>
+        <v>1.5598</v>
       </c>
       <c r="E18" t="n">
-        <v>5.0533</v>
+        <v>5.0295</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6658</v>
+        <v>4.642</v>
       </c>
       <c r="G18" t="n">
         <v>0.3875</v>
       </c>
       <c r="H18" t="n">
-        <v>5.0129</v>
+        <v>4.9755</v>
       </c>
       <c r="I18" t="n">
         <v>5.0596</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.0408</v>
+        <v>5.0274</v>
       </c>
       <c r="C19" t="n">
-        <v>3.3768</v>
+        <v>3.3678</v>
       </c>
       <c r="D19" t="n">
-        <v>1.615</v>
+        <v>1.559</v>
       </c>
       <c r="E19" t="n">
-        <v>5.0408</v>
+        <v>5.0274</v>
       </c>
       <c r="F19" t="n">
-        <v>5.0408</v>
+        <v>5.0274</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6009</v>
+        <v>5.58</v>
       </c>
       <c r="I19" t="n">
         <v>5.6269</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.5741</v>
+        <v>4.5502</v>
       </c>
       <c r="C20" t="n">
-        <v>3.0641</v>
+        <v>3.0481</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4265</v>
+        <v>1.3689</v>
       </c>
       <c r="E20" t="n">
-        <v>4.5741</v>
+        <v>4.5502</v>
       </c>
       <c r="F20" t="n">
-        <v>4.6866</v>
+        <v>4.6627</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1125</v>
       </c>
       <c r="H20" t="n">
-        <v>5.0456</v>
+        <v>5.008</v>
       </c>
       <c r="I20" t="n">
         <v>5.0927</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.4852</v>
+        <v>4.4737</v>
       </c>
       <c r="C21" t="n">
-        <v>3.0046</v>
+        <v>2.9969</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3906</v>
+        <v>1.3384</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4852</v>
+        <v>4.4737</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5449</v>
+        <v>4.5334</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0597</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8233</v>
+        <v>4.8053</v>
       </c>
       <c r="I21" t="n">
         <v>4.8458</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.4256</v>
+        <v>4.4146</v>
       </c>
       <c r="C22" t="n">
-        <v>2.9646</v>
+        <v>2.9573</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3665</v>
+        <v>1.3149</v>
       </c>
       <c r="E22" t="n">
-        <v>4.4256</v>
+        <v>4.4146</v>
       </c>
       <c r="F22" t="n">
-        <v>4.4256</v>
+        <v>4.4146</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6364</v>
+        <v>4.6191</v>
       </c>
       <c r="I22" t="n">
         <v>4.6579</v>
@@ -1468,7 +1468,7 @@
         <v>2.8098</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2731</v>
+        <v>1.2272</v>
       </c>
       <c r="E23" t="n">
         <v>4.1945</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.9855</v>
+        <v>3.9583</v>
       </c>
       <c r="C24" t="n">
-        <v>2.6698</v>
+        <v>2.6516</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1887</v>
+        <v>1.1331</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9855</v>
+        <v>3.9583</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6582</v>
+        <v>3.631</v>
       </c>
       <c r="G24" t="n">
         <v>0.3273</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6582</v>
+        <v>3.631</v>
       </c>
       <c r="I24" t="n">
         <v>3.6923</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.9264</v>
+        <v>3.9148</v>
       </c>
       <c r="C25" t="n">
-        <v>2.6302</v>
+        <v>2.6225</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1648</v>
+        <v>1.1157</v>
       </c>
       <c r="E25" t="n">
-        <v>3.9264</v>
+        <v>3.9148</v>
       </c>
       <c r="F25" t="n">
-        <v>4.5639</v>
+        <v>4.5523</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6375</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8531</v>
+        <v>4.835</v>
       </c>
       <c r="I25" t="n">
         <v>4.8757</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.8838</v>
+        <v>3.8709</v>
       </c>
       <c r="C26" t="n">
-        <v>2.6017</v>
+        <v>2.5931</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1476</v>
+        <v>1.0983</v>
       </c>
       <c r="E26" t="n">
-        <v>3.8838</v>
+        <v>3.8709</v>
       </c>
       <c r="F26" t="n">
-        <v>3.4576</v>
+        <v>3.4447</v>
       </c>
       <c r="G26" t="n">
         <v>0.4262</v>
       </c>
       <c r="H26" t="n">
-        <v>3.4576</v>
+        <v>3.4447</v>
       </c>
       <c r="I26" t="n">
         <v>3.4737</v>
@@ -1652,7 +1652,7 @@
         <v>2.4967</v>
       </c>
       <c r="D27" t="n">
-        <v>1.0843</v>
+        <v>1.0409</v>
       </c>
       <c r="E27" t="n">
         <v>3.727</v>
@@ -1698,7 +1698,7 @@
         <v>2.3522</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9972</v>
+        <v>0.955</v>
       </c>
       <c r="E28" t="n">
         <v>3.5114</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.51</v>
+        <v>3.4969</v>
       </c>
       <c r="C29" t="n">
-        <v>2.3513</v>
+        <v>2.3425</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9966</v>
+        <v>0.9493</v>
       </c>
       <c r="E29" t="n">
-        <v>3.51</v>
+        <v>3.4969</v>
       </c>
       <c r="F29" t="n">
-        <v>3.51</v>
+        <v>3.4969</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.51</v>
+        <v>3.4969</v>
       </c>
       <c r="I29" t="n">
         <v>3.5264</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.5028</v>
+        <v>3.4786</v>
       </c>
       <c r="C30" t="n">
-        <v>2.3465</v>
+        <v>2.3303</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9937</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>3.5028</v>
+        <v>3.4786</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2494</v>
+        <v>3.2252</v>
       </c>
       <c r="G30" t="n">
         <v>0.2534</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2494</v>
+        <v>3.2252</v>
       </c>
       <c r="I30" t="n">
         <v>3.2797</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.4715</v>
+        <v>3.4634</v>
       </c>
       <c r="C31" t="n">
-        <v>2.3255</v>
+        <v>2.3201</v>
       </c>
       <c r="D31" t="n">
-        <v>0.981</v>
+        <v>0.9359</v>
       </c>
       <c r="E31" t="n">
-        <v>3.4715</v>
+        <v>3.4634</v>
       </c>
       <c r="F31" t="n">
-        <v>3.1057</v>
+        <v>4.2301</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3658</v>
+        <v>-0.7667</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1057</v>
+        <v>4.3297</v>
       </c>
       <c r="I31" t="n">
-        <v>3.1201</v>
+        <v>4.3297</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3658</v>
+        <v>-0.7667</v>
       </c>
       <c r="K31" t="n">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="L31" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4859</v>
+        <v>3.563</v>
       </c>
       <c r="N31" t="n">
-        <v>405</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.4634</v>
+        <v>3.4599</v>
       </c>
       <c r="C32" t="n">
-        <v>2.3201</v>
+        <v>2.3177</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9778</v>
+        <v>0.9345</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4634</v>
+        <v>3.4599</v>
       </c>
       <c r="F32" t="n">
-        <v>4.2301</v>
+        <v>3.0941</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7667</v>
+        <v>0.3658</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3297</v>
+        <v>3.0941</v>
       </c>
       <c r="I32" t="n">
-        <v>4.3297</v>
+        <v>3.1201</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7667</v>
+        <v>0.3658</v>
       </c>
       <c r="K32" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="L32" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.563</v>
+        <v>3.4859</v>
       </c>
       <c r="N32" t="n">
-        <v>375</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33">
@@ -1928,7 +1928,7 @@
         <v>2.2341</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.8848</v>
       </c>
       <c r="E33" t="n">
         <v>3.335</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.3076</v>
+        <v>3.2953</v>
       </c>
       <c r="C34" t="n">
-        <v>2.2157</v>
+        <v>2.2075</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.8689</v>
       </c>
       <c r="E34" t="n">
-        <v>3.3076</v>
+        <v>3.2953</v>
       </c>
       <c r="F34" t="n">
-        <v>3.3076</v>
+        <v>3.2953</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.3076</v>
+        <v>3.2953</v>
       </c>
       <c r="I34" t="n">
         <v>3.323</v>
@@ -2020,7 +2020,7 @@
         <v>2.1919</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9005</v>
+        <v>0.8597</v>
       </c>
       <c r="E35" t="n">
         <v>3.2721</v>
@@ -2066,7 +2066,7 @@
         <v>2.1793</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8929</v>
+        <v>0.8522</v>
       </c>
       <c r="E36" t="n">
         <v>3.2532</v>
@@ -2112,7 +2112,7 @@
         <v>2.1221</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8182</v>
       </c>
       <c r="E37" t="n">
         <v>3.1679</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.1021</v>
+        <v>3.0896</v>
       </c>
       <c r="C38" t="n">
-        <v>2.0781</v>
+        <v>2.0697</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8318</v>
+        <v>0.787</v>
       </c>
       <c r="E38" t="n">
-        <v>3.1021</v>
+        <v>3.0896</v>
       </c>
       <c r="F38" t="n">
-        <v>3.3365</v>
+        <v>3.324</v>
       </c>
       <c r="G38" t="n">
         <v>-0.2344</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3365</v>
+        <v>3.324</v>
       </c>
       <c r="I38" t="n">
         <v>3.352</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.0319</v>
+        <v>3.0206</v>
       </c>
       <c r="C39" t="n">
-        <v>2.031</v>
+        <v>2.0235</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8035</v>
+        <v>0.7595</v>
       </c>
       <c r="E39" t="n">
-        <v>3.0319</v>
+        <v>3.0206</v>
       </c>
       <c r="F39" t="n">
-        <v>3.0319</v>
+        <v>3.0206</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.0319</v>
+        <v>3.0206</v>
       </c>
       <c r="I39" t="n">
         <v>3.046</v>
@@ -2250,7 +2250,7 @@
         <v>1.7763</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6499</v>
+        <v>0.6125</v>
       </c>
       <c r="E40" t="n">
         <v>2.6517</v>
@@ -2296,7 +2296,7 @@
         <v>1.7691</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6455</v>
+        <v>0.6082</v>
       </c>
       <c r="E41" t="n">
         <v>2.6409</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.5656</v>
+        <v>2.5458</v>
       </c>
       <c r="C42" t="n">
-        <v>1.7187</v>
+        <v>1.7054</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6151</v>
+        <v>0.5703</v>
       </c>
       <c r="E42" t="n">
-        <v>2.5656</v>
+        <v>2.5458</v>
       </c>
       <c r="F42" t="n">
-        <v>4.1268</v>
+        <v>4.107</v>
       </c>
       <c r="G42" t="n">
         <v>-1.5612</v>
       </c>
       <c r="H42" t="n">
-        <v>4.1677</v>
+        <v>4.1367</v>
       </c>
       <c r="I42" t="n">
         <v>4.2066</v>
@@ -2388,7 +2388,7 @@
         <v>1.688</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5966</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E43" t="n">
         <v>2.5199</v>
@@ -2434,7 +2434,7 @@
         <v>1.6334</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5637</v>
+        <v>0.5275</v>
       </c>
       <c r="E44" t="n">
         <v>2.4383</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.4014</v>
+        <v>2.3924</v>
       </c>
       <c r="C45" t="n">
-        <v>1.6087</v>
+        <v>1.6026</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5488</v>
+        <v>0.5092</v>
       </c>
       <c r="E45" t="n">
-        <v>2.4014</v>
+        <v>2.3924</v>
       </c>
       <c r="F45" t="n">
-        <v>2.4014</v>
+        <v>2.3924</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.4014</v>
+        <v>2.3924</v>
       </c>
       <c r="I45" t="n">
         <v>2.4126</v>
@@ -2526,7 +2526,7 @@
         <v>1.49</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4772</v>
+        <v>0.4423</v>
       </c>
       <c r="E46" t="n">
         <v>2.2243</v>
@@ -2572,7 +2572,7 @@
         <v>1.4851</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4742</v>
+        <v>0.4393</v>
       </c>
       <c r="E47" t="n">
         <v>2.2169</v>
@@ -2618,7 +2618,7 @@
         <v>1.4601</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4591</v>
+        <v>0.4244</v>
       </c>
       <c r="E48" t="n">
         <v>2.1796</v>
@@ -2664,7 +2664,7 @@
         <v>1.4527</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4547</v>
+        <v>0.4201</v>
       </c>
       <c r="E49" t="n">
         <v>2.1686</v>
@@ -2710,7 +2710,7 @@
         <v>1.3893</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4164</v>
+        <v>0.3823</v>
       </c>
       <c r="E50" t="n">
         <v>2.0739</v>
@@ -2756,7 +2756,7 @@
         <v>1.3141</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3711</v>
+        <v>0.3376</v>
       </c>
       <c r="E51" t="n">
         <v>1.9617</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.9382</v>
+        <v>1.931</v>
       </c>
       <c r="C52" t="n">
-        <v>1.2984</v>
+        <v>1.2935</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3616</v>
+        <v>0.3254</v>
       </c>
       <c r="E52" t="n">
-        <v>1.9382</v>
+        <v>1.931</v>
       </c>
       <c r="F52" t="n">
-        <v>1.9382</v>
+        <v>1.931</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.9382</v>
+        <v>1.931</v>
       </c>
       <c r="I52" t="n">
         <v>1.9472</v>
@@ -2848,7 +2848,7 @@
         <v>1.2781</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3494</v>
+        <v>0.3162</v>
       </c>
       <c r="E53" t="n">
         <v>1.908</v>
@@ -2894,7 +2894,7 @@
         <v>1.268</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3433</v>
+        <v>0.3102</v>
       </c>
       <c r="E54" t="n">
         <v>1.8929</v>
@@ -2940,7 +2940,7 @@
         <v>1.2499</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3324</v>
+        <v>0.2994</v>
       </c>
       <c r="E55" t="n">
         <v>1.8658</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.8543</v>
+        <v>1.8474</v>
       </c>
       <c r="C56" t="n">
-        <v>1.2422</v>
+        <v>1.2375</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3277</v>
+        <v>0.2921</v>
       </c>
       <c r="E56" t="n">
-        <v>1.8543</v>
+        <v>1.8474</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8543</v>
+        <v>1.8474</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.8543</v>
+        <v>1.8474</v>
       </c>
       <c r="I56" t="n">
         <v>1.8629</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.6601</v>
+        <v>1.6539</v>
       </c>
       <c r="C57" t="n">
-        <v>1.1121</v>
+        <v>1.1079</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2493</v>
+        <v>0.215</v>
       </c>
       <c r="E57" t="n">
-        <v>1.6601</v>
+        <v>1.6539</v>
       </c>
       <c r="F57" t="n">
-        <v>1.6601</v>
+        <v>1.6539</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1.6601</v>
+        <v>1.6539</v>
       </c>
       <c r="I57" t="n">
         <v>1.6678</v>
@@ -3078,7 +3078,7 @@
         <v>1.1033</v>
       </c>
       <c r="D58" t="n">
-        <v>0.244</v>
+        <v>0.2123</v>
       </c>
       <c r="E58" t="n">
         <v>1.647</v>
@@ -3124,7 +3124,7 @@
         <v>1.0695</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2236</v>
+        <v>0.1922</v>
       </c>
       <c r="E59" t="n">
         <v>1.5966</v>
@@ -3170,7 +3170,7 @@
         <v>1.0391</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2053</v>
+        <v>0.1741</v>
       </c>
       <c r="E60" t="n">
         <v>1.5512</v>
@@ -3216,7 +3216,7 @@
         <v>0.9727</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1653</v>
+        <v>0.1346</v>
       </c>
       <c r="E61" t="n">
         <v>1.4521</v>
@@ -3262,7 +3262,7 @@
         <v>0.9571</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1558</v>
+        <v>0.1253</v>
       </c>
       <c r="E62" t="n">
         <v>1.4288</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.4233</v>
+        <v>1.418</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9534</v>
+        <v>0.9499</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1536</v>
+        <v>0.121</v>
       </c>
       <c r="E63" t="n">
-        <v>1.4233</v>
+        <v>1.418</v>
       </c>
       <c r="F63" t="n">
-        <v>1.4233</v>
+        <v>1.418</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.4233</v>
+        <v>1.418</v>
       </c>
       <c r="I63" t="n">
         <v>1.4299</v>
@@ -3354,7 +3354,7 @@
         <v>0.9184</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1325</v>
+        <v>0.1023</v>
       </c>
       <c r="E64" t="n">
         <v>1.371</v>
@@ -3400,7 +3400,7 @@
         <v>0.8784</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1084</v>
+        <v>0.0785</v>
       </c>
       <c r="E65" t="n">
         <v>1.3113</v>
@@ -3446,7 +3446,7 @@
         <v>0.8756</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1067</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>1.3071</v>
@@ -3492,7 +3492,7 @@
         <v>0.855</v>
       </c>
       <c r="D67" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="E67" t="n">
         <v>1.2764</v>
@@ -3538,7 +3538,7 @@
         <v>0.7594</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0366</v>
+        <v>0.0078</v>
       </c>
       <c r="E68" t="n">
         <v>1.1337</v>
@@ -3584,7 +3584,7 @@
         <v>0.7221</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0141</v>
+        <v>-0.0145</v>
       </c>
       <c r="E69" t="n">
         <v>1.0779</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8222</v>
+        <v>0.8336</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5508</v>
+        <v>0.5584</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.0892</v>
+        <v>-0.1118</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8222</v>
+        <v>0.8336</v>
       </c>
       <c r="F70" t="n">
-        <v>-3.0579</v>
+        <v>-3.0465</v>
       </c>
       <c r="G70" t="n">
         <v>3.8801</v>
       </c>
       <c r="H70" t="n">
-        <v>-3.0579</v>
+        <v>-3.0465</v>
       </c>
       <c r="I70" t="n">
         <v>-3.0721</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5457</v>
+        <v>0.5436</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3656</v>
+        <v>0.3641</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2009</v>
+        <v>-0.2273</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5457</v>
+        <v>0.5436</v>
       </c>
       <c r="F71" t="n">
-        <v>0.5457</v>
+        <v>0.5436</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5457</v>
+        <v>0.5436</v>
       </c>
       <c r="I71" t="n">
         <v>0.5482</v>
@@ -3722,7 +3722,7 @@
         <v>0.3278</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.2237</v>
+        <v>-0.2489</v>
       </c>
       <c r="E72" t="n">
         <v>0.4894</v>
@@ -3768,7 +3768,7 @@
         <v>0.3233</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.2264</v>
+        <v>-0.2516</v>
       </c>
       <c r="E73" t="n">
         <v>0.4826</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4628</v>
+        <v>0.4611</v>
       </c>
       <c r="C74" t="n">
-        <v>0.31</v>
+        <v>0.3089</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.2344</v>
+        <v>-0.2602</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4628</v>
+        <v>0.4611</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4628</v>
+        <v>0.4611</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.4628</v>
+        <v>0.4611</v>
       </c>
       <c r="I74" t="n">
         <v>0.465</v>
@@ -3860,7 +3860,7 @@
         <v>0.2991</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.241</v>
+        <v>-0.266</v>
       </c>
       <c r="E75" t="n">
         <v>0.4465</v>
@@ -3906,7 +3906,7 @@
         <v>0.2628</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.2629</v>
+        <v>-0.2876</v>
       </c>
       <c r="E76" t="n">
         <v>0.3923</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3844</v>
+        <v>0.3796</v>
       </c>
       <c r="C77" t="n">
-        <v>0.2575</v>
+        <v>0.2543</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.2661</v>
+        <v>-0.2927</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3844</v>
+        <v>0.3796</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6452</v>
+        <v>0.6404</v>
       </c>
       <c r="G77" t="n">
         <v>-0.2608</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6452</v>
+        <v>0.6404</v>
       </c>
       <c r="I77" t="n">
         <v>0.6512</v>
@@ -3998,7 +3998,7 @@
         <v>0.2448</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.2737</v>
+        <v>-0.2983</v>
       </c>
       <c r="E78" t="n">
         <v>0.3655</v>
@@ -4044,7 +4044,7 @@
         <v>0.2255</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2854</v>
+        <v>-0.3098</v>
       </c>
       <c r="E79" t="n">
         <v>0.3366</v>
@@ -4090,7 +4090,7 @@
         <v>0.2125</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.2932</v>
+        <v>-0.3175</v>
       </c>
       <c r="E80" t="n">
         <v>0.3172</v>
@@ -4136,7 +4136,7 @@
         <v>0.0607</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.3848</v>
+        <v>-0.4078</v>
       </c>
       <c r="E81" t="n">
         <v>0.0906</v>
@@ -4182,7 +4182,7 @@
         <v>0.0492</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.3917</v>
+        <v>-0.4147</v>
       </c>
       <c r="E82" t="n">
         <v>0.07340000000000001</v>
@@ -4228,7 +4228,7 @@
         <v>0.0373</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.3989</v>
+        <v>-0.4217</v>
       </c>
       <c r="E83" t="n">
         <v>0.0557</v>
@@ -4274,7 +4274,7 @@
         <v>-0.08649999999999999</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.4735</v>
+        <v>-0.4953</v>
       </c>
       <c r="E84" t="n">
         <v>-0.1291</v>
@@ -4320,7 +4320,7 @@
         <v>-0.1612</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="E85" t="n">
         <v>-0.2407</v>
@@ -4366,7 +4366,7 @@
         <v>-0.376</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.6481</v>
+        <v>-0.6675</v>
       </c>
       <c r="E86" t="n">
         <v>-0.5613</v>
@@ -4412,7 +4412,7 @@
         <v>-0.4537</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.695</v>
+        <v>-0.7137</v>
       </c>
       <c r="E87" t="n">
         <v>-0.6773</v>
@@ -4458,7 +4458,7 @@
         <v>-0.4662</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.7025</v>
+        <v>-0.7212</v>
       </c>
       <c r="E88" t="n">
         <v>-0.6959</v>
@@ -4504,7 +4504,7 @@
         <v>-0.5004</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.7231</v>
+        <v>-0.7415</v>
       </c>
       <c r="E89" t="n">
         <v>-0.747</v>
@@ -4550,7 +4550,7 @@
         <v>-0.5336</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.7432</v>
+        <v>-0.7613</v>
       </c>
       <c r="E90" t="n">
         <v>-0.7966</v>
@@ -4596,7 +4596,7 @@
         <v>-0.5904</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.7774</v>
+        <v>-0.795</v>
       </c>
       <c r="E91" t="n">
         <v>-0.8813</v>
@@ -4642,7 +4642,7 @@
         <v>-0.6683</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.8244</v>
+        <v>-0.8414</v>
       </c>
       <c r="E92" t="n">
         <v>-0.9977</v>
@@ -4688,7 +4688,7 @@
         <v>-0.7513</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.8908</v>
       </c>
       <c r="E93" t="n">
         <v>-1.1216</v>
@@ -4734,7 +4734,7 @@
         <v>-0.7625</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.8812</v>
+        <v>-0.8974</v>
       </c>
       <c r="E94" t="n">
         <v>-1.1383</v>
@@ -4780,7 +4780,7 @@
         <v>-0.773</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.8875</v>
+        <v>-0.9036</v>
       </c>
       <c r="E95" t="n">
         <v>-1.1539</v>
@@ -4826,7 +4826,7 @@
         <v>-0.9863</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.0161</v>
+        <v>-1.0305</v>
       </c>
       <c r="E96" t="n">
         <v>-1.4723</v>
@@ -4866,25 +4866,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-1.699</v>
+        <v>-1.6927</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.1381</v>
+        <v>-1.1339</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.1077</v>
+        <v>-1.1183</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.699</v>
+        <v>-1.6927</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.699</v>
+        <v>-1.6927</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.699</v>
+        <v>-1.6927</v>
       </c>
       <c r="I97" t="n">
         <v>-1.7069</v>
@@ -4918,7 +4918,7 @@
         <v>-1.164</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.1233</v>
+        <v>-1.1362</v>
       </c>
       <c r="E98" t="n">
         <v>-1.7376</v>
@@ -4958,25 +4958,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.8491</v>
+        <v>-1.8538</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.2387</v>
+        <v>-1.2418</v>
       </c>
       <c r="D99" t="n">
-        <v>-1.1684</v>
+        <v>-1.1825</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.8491</v>
+        <v>-1.8538</v>
       </c>
       <c r="F99" t="n">
-        <v>0.633</v>
+        <v>0.6283</v>
       </c>
       <c r="G99" t="n">
         <v>-2.4821</v>
       </c>
       <c r="H99" t="n">
-        <v>0.633</v>
+        <v>0.6283</v>
       </c>
       <c r="I99" t="n">
         <v>0.6389</v>
@@ -5010,7 +5010,7 @@
         <v>-1.2651</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.1843</v>
+        <v>-1.1963</v>
       </c>
       <c r="E100" t="n">
         <v>-1.8885</v>
@@ -5056,7 +5056,7 @@
         <v>-1.2839</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.1956</v>
+        <v>-1.2075</v>
       </c>
       <c r="E101" t="n">
         <v>-1.9166</v>
@@ -5096,25 +5096,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-2.0389</v>
+        <v>-2.0301</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.3658</v>
+        <v>-1.3599</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.245</v>
+        <v>-1.2527</v>
       </c>
       <c r="E102" t="n">
-        <v>-2.0389</v>
+        <v>-2.0301</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.1813</v>
+        <v>-1.1725</v>
       </c>
       <c r="G102" t="n">
         <v>-0.8576</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.1813</v>
+        <v>-1.1725</v>
       </c>
       <c r="I102" t="n">
         <v>-1.1923</v>
@@ -5148,7 +5148,7 @@
         <v>-1.5066</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.3299</v>
+        <v>-1.3399</v>
       </c>
       <c r="E103" t="n">
         <v>-2.249</v>
@@ -5194,7 +5194,7 @@
         <v>-1.507</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.3302</v>
+        <v>-1.3402</v>
       </c>
       <c r="E104" t="n">
         <v>-2.2497</v>
@@ -5240,7 +5240,7 @@
         <v>-1.5403</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.3502</v>
+        <v>-1.36</v>
       </c>
       <c r="E105" t="n">
         <v>-2.2993</v>
@@ -5286,7 +5286,7 @@
         <v>-1.6145</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.395</v>
+        <v>-1.4041</v>
       </c>
       <c r="E106" t="n">
         <v>-2.4101</v>
@@ -5332,7 +5332,7 @@
         <v>-1.639</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.4098</v>
+        <v>-1.4187</v>
       </c>
       <c r="E107" t="n">
         <v>-2.4467</v>
@@ -5378,7 +5378,7 @@
         <v>-1.6579</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.4212</v>
+        <v>-1.4299</v>
       </c>
       <c r="E108" t="n">
         <v>-2.4749</v>
@@ -5424,7 +5424,7 @@
         <v>-1.6748</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.4313</v>
+        <v>-1.44</v>
       </c>
       <c r="E109" t="n">
         <v>-2.5001</v>
@@ -5470,7 +5470,7 @@
         <v>-1.986</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.619</v>
+        <v>-1.625</v>
       </c>
       <c r="E110" t="n">
         <v>-2.9647</v>
@@ -5516,7 +5516,7 @@
         <v>-2.006</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.6311</v>
+        <v>-1.6369</v>
       </c>
       <c r="E111" t="n">
         <v>-2.9945</v>
@@ -5562,7 +5562,7 @@
         <v>-2.0825</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.6772</v>
+        <v>-1.6825</v>
       </c>
       <c r="E112" t="n">
         <v>-3.1088</v>
@@ -5608,7 +5608,7 @@
         <v>-2.3061</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.8121</v>
+        <v>-1.8154</v>
       </c>
       <c r="E113" t="n">
         <v>-3.4426</v>
@@ -5654,7 +5654,7 @@
         <v>-2.5677</v>
       </c>
       <c r="D114" t="n">
-        <v>-1.9698</v>
+        <v>-1.971</v>
       </c>
       <c r="E114" t="n">
         <v>-3.833</v>
@@ -5700,7 +5700,7 @@
         <v>-2.5812</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.978</v>
+        <v>-1.979</v>
       </c>
       <c r="E115" t="n">
         <v>-3.8532</v>
@@ -5746,7 +5746,7 @@
         <v>-2.6649</v>
       </c>
       <c r="D116" t="n">
-        <v>-2.0284</v>
+        <v>-2.0288</v>
       </c>
       <c r="E116" t="n">
         <v>-3.9781</v>
@@ -5792,7 +5792,7 @@
         <v>-2.8231</v>
       </c>
       <c r="D117" t="n">
-        <v>-2.1238</v>
+        <v>-2.1229</v>
       </c>
       <c r="E117" t="n">
         <v>-4.2143</v>
@@ -5838,7 +5838,7 @@
         <v>-2.8248</v>
       </c>
       <c r="D118" t="n">
-        <v>-2.1249</v>
+        <v>-2.1239</v>
       </c>
       <c r="E118" t="n">
         <v>-4.2168</v>
@@ -5878,25 +5878,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-5.2125</v>
+        <v>-5.1797</v>
       </c>
       <c r="C119" t="n">
-        <v>-3.4918</v>
+        <v>-3.4698</v>
       </c>
       <c r="D119" t="n">
-        <v>-2.5271</v>
+        <v>-2.5075</v>
       </c>
       <c r="E119" t="n">
-        <v>-5.2125</v>
+        <v>-5.1797</v>
       </c>
       <c r="F119" t="n">
-        <v>-4.4033</v>
+        <v>-4.3705</v>
       </c>
       <c r="G119" t="n">
         <v>-0.8092</v>
       </c>
       <c r="H119" t="n">
-        <v>-4.4033</v>
+        <v>-4.3705</v>
       </c>
       <c r="I119" t="n">
         <v>-4.4444</v>
@@ -5930,7 +5930,7 @@
         <v>-4.2015</v>
       </c>
       <c r="D120" t="n">
-        <v>-2.9551</v>
+        <v>-2.9427</v>
       </c>
       <c r="E120" t="n">
         <v>-6.272</v>
@@ -5970,25 +5970,25 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-7.3004</v>
+        <v>-7.2843</v>
       </c>
       <c r="C121" t="n">
-        <v>-4.8904</v>
+        <v>-4.8796</v>
       </c>
       <c r="D121" t="n">
-        <v>-3.3706</v>
+        <v>-3.346</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.3004</v>
+        <v>-7.2843</v>
       </c>
       <c r="F121" t="n">
-        <v>-4.3004</v>
+        <v>-4.2843</v>
       </c>
       <c r="G121" t="n">
         <v>-3</v>
       </c>
       <c r="H121" t="n">
-        <v>-4.3004</v>
+        <v>-4.2843</v>
       </c>
       <c r="I121" t="n">
         <v>-4.3204</v>
